--- a/exports/red5-dhcp_switchboard.xlsx
+++ b/exports/red5-dhcp_switchboard.xlsx
@@ -496,7 +496,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27  ·  source: E-01 / E-02 / 13-4 動力盤改造図</t>
+          <t>Generated 2026-07-30  ·  source: E-01 / E-02 / 13-4 動力盤改造図</t>
         </is>
       </c>
     </row>
